--- a/HP.xlsx
+++ b/HP.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\JOB\REPO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B772062-7FD3-4EA3-A669-1D32F688C508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{270EC4E5-B157-491E-919F-80498AAAE8BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20400" yWindow="750" windowWidth="15375" windowHeight="10080" activeTab="1" xr2:uid="{61A23AE0-FA6B-4D65-8B38-B2760B7E9AD5}"/>
+    <workbookView xWindow="-20130" yWindow="750" windowWidth="15375" windowHeight="10080" activeTab="2" xr2:uid="{61A23AE0-FA6B-4D65-8B38-B2760B7E9AD5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="97">
   <si>
     <t>はい。では **STEP 4「HTML側で新しいJSON形式を受け取る」**へ進みます。</t>
   </si>
@@ -518,6 +519,214 @@
         <scheme val="minor"/>
       </rPr>
       <t>へ進みましょう。</t>
+    </r>
+  </si>
+  <si>
+    <t>ただし、1点だけ確認が必要です</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">この </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>Code.gs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 側では、</t>
+    </r>
+  </si>
+  <si>
+    <t>e.parameter.startHour</t>
+  </si>
+  <si>
+    <t>e.parameter.endHour</t>
+  </si>
+  <si>
+    <t>という名前で受け取る想定です。</t>
+  </si>
+  <si>
+    <r>
+      <t>したがって、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">HTMLの予約送信側が実際に </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>startHour</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> と </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>endHour</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> という名前で送っている必要があります。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">以前の予約フォームでは </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>startHour</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>endHour</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> を使っていた構成なので、おそらくこのままで合います。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>もしよければ次に、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>現在のHTMLの「予約送信部分」も貼ってください。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>そこまで確認すれば、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>Code.gs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → HTML → スプレッドシート → 店舗メール → お客様メールまで、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>開始・終了時刻が一本につながっているか</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を確認できます。</t>
     </r>
   </si>
 </sst>
@@ -1609,4 +1818,60 @@
   <phoneticPr fontId="6"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5448B849-D88B-4116-9D41-4E7D4FE612FA}">
+  <dimension ref="C3:C17"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="3" spans="3:3" ht="22.5">
+      <c r="C3" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3">
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3">
+      <c r="C7" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3">
+      <c r="C8" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3">
+      <c r="C10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="3:3">
+      <c r="C12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="3:3">
+      <c r="C14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="3:3">
+      <c r="C16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>